--- a/Assets/ExcelDatas/SkillData.xlsx
+++ b/Assets/ExcelDatas/SkillData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Project_Advence-main\Assets\ExcelDatas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ProjectGit\Project_Advence_g\Assets\ExcelDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4DC643-D0C6-4B55-8AD8-C2DB61A3EA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD822F3-B2F9-4E87-85E4-E6A962D0F2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15840" xr2:uid="{00B68857-C6E1-4D98-82FE-3C4F502D76E8}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{00B68857-C6E1-4D98-82FE-3C4F502D76E8}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillTable" sheetId="3" r:id="rId1"/>
@@ -846,8 +846,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}" name="표2" displayName="표2" ref="A3:M15" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="A3:M15" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}" name="표2" displayName="표2" ref="A3:M16" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A3:M16" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{513471B3-6400-4B91-8068-618BE05D815D}" name="Index" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{CD7519DA-C7A5-4013-9D1E-02930E6F874D}" name="Name" dataDxfId="19"/>
@@ -1179,7 +1179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A9E828-B25D-49C6-B4AF-221979A45248}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.125" style="1" bestFit="1" customWidth="1"/>
@@ -1811,6 +1811,10 @@
       <c r="M15" s="1" t="s">
         <v>52</v>
       </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/ExcelDatas/SkillData.xlsx
+++ b/Assets/ExcelDatas/SkillData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ProjectGit\Project_Advence_g\Assets\ExcelDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD822F3-B2F9-4E87-85E4-E6A962D0F2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBDDE7F-CBF1-4DBC-8639-DFDC1095F392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{00B68857-C6E1-4D98-82FE-3C4F502D76E8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="83">
   <si>
     <t>ALL</t>
   </si>
@@ -198,27 +198,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>워터벌룬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일정 시간 뒤 범위에 공격을 가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Waterballoon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SPUM/0_Flat/Icon_Flat__31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skills/WaterBalloon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -846,8 +826,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}" name="표2" displayName="표2" ref="A3:M16" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="A3:M16" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}" name="표2" displayName="표2" ref="A3:M15" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A3:M15" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{513471B3-6400-4B91-8068-618BE05D815D}" name="Index" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{CD7519DA-C7A5-4013-9D1E-02930E6F874D}" name="Name" dataDxfId="19"/>
@@ -1179,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A9E828-B25D-49C6-B4AF-221979A45248}">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.125" style="1" bestFit="1" customWidth="1"/>
@@ -1217,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>0</v>
@@ -1258,7 +1238,7 @@
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>40</v>
@@ -1299,10 +1279,10 @@
         <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>4</v>
@@ -1317,7 +1297,7 @@
         <v>23</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1340,7 +1320,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H4" s="1">
         <v>1.5</v>
@@ -1381,7 +1361,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H5" s="1">
         <v>2</v>
@@ -1407,10 +1387,10 @@
         <v>10003</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>29</v>
@@ -1422,7 +1402,7 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H6" s="1">
         <v>1.5</v>
@@ -1448,13 +1428,13 @@
         <v>10004</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1463,7 +1443,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H7" s="1">
         <v>1.5</v>
@@ -1478,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>42</v>
@@ -1489,13 +1469,13 @@
         <v>10005</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1504,7 +1484,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H8" s="1">
         <v>1.5</v>
@@ -1519,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>42</v>
@@ -1533,10 +1513,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1545,7 +1525,7 @@
         <v>0.5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H9" s="1">
         <v>1.5</v>
@@ -1560,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>42</v>
@@ -1571,13 +1551,13 @@
         <v>10007</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1">
         <v>1.7</v>
@@ -1586,7 +1566,7 @@
         <v>0.5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H10" s="1">
         <v>2</v>
@@ -1601,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>42</v>
@@ -1612,13 +1592,13 @@
         <v>10008</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E11" s="1">
         <v>1.7</v>
@@ -1627,7 +1607,7 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H11" s="1">
         <v>2</v>
@@ -1642,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>42</v>
@@ -1650,95 +1630,95 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>10009</v>
+        <v>10010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="E12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H12" s="1">
         <v>1.5</v>
       </c>
       <c r="I12" s="1">
+        <v>18</v>
+      </c>
+      <c r="J12" s="1">
         <v>12</v>
       </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>10010</v>
+        <v>10011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="1">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H13" s="1">
         <v>1.5</v>
       </c>
       <c r="I13" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J13" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>10011</v>
+        <v>10012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>29</v>
@@ -1750,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H14" s="1">
         <v>1.5</v>
@@ -1765,56 +1745,15 @@
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>10012</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="1">
-        <v>2</v>
-      </c>
-      <c r="F15" s="1">
-        <v>2</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="I15" s="1">
-        <v>12</v>
-      </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1896,7 +1835,7 @@
         <v>37</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
